--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2024_biobio.xlsx
@@ -146,7 +146,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 02:10</t>
+    <t xml:space="preserve">2026-08-17 18:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2024_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_d_otras_relaciones_a_2024_biobio.xlsx
@@ -146,7 +146,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 18:08</t>
+    <t xml:space="preserve">2026-09-06 22:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
